--- a/23_AI_Gen/Attendance_latest.xlsx
+++ b/23_AI_Gen/Attendance_latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\23_AI_Gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{004052C3-2521-4405-8DCF-DCE1A86FA7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF1BED7-3172-49A6-A14C-64D12F33AD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2B33F4A9-8A1F-4F27-B2E0-7FFE4ED6D1CE}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="60">
   <si>
     <t>Ayush</t>
   </si>
   <si>
-    <t>Gupta</t>
-  </si>
-  <si>
     <t>Sahil</t>
   </si>
   <si>
@@ -46,6 +43,168 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Mitanshu</t>
+  </si>
+  <si>
+    <t>Panchal</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>Devanshi</t>
+  </si>
+  <si>
+    <t>Trivedi</t>
+  </si>
+  <si>
+    <t>Surat</t>
+  </si>
+  <si>
+    <t>Dhruvi</t>
+  </si>
+  <si>
+    <t>Dhruvin</t>
+  </si>
+  <si>
+    <t>Hani</t>
+  </si>
+  <si>
+    <t>Prajapati</t>
+  </si>
+  <si>
+    <t>Hardik</t>
+  </si>
+  <si>
+    <t>Songara</t>
+  </si>
+  <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>Kewalramani</t>
+  </si>
+  <si>
+    <t>Vaghamshi</t>
+  </si>
+  <si>
+    <t>Harshil</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>Nasriwala</t>
+  </si>
+  <si>
+    <t>Jenish</t>
+  </si>
+  <si>
+    <t>Rami</t>
+  </si>
+  <si>
+    <t>Khushi</t>
+  </si>
+  <si>
+    <t>Barvaliya</t>
+  </si>
+  <si>
+    <t>Kishan</t>
+  </si>
+  <si>
+    <t>Sapariya</t>
+  </si>
+  <si>
+    <t>Mohammedafzal</t>
+  </si>
+  <si>
+    <t>Diwan</t>
+  </si>
+  <si>
+    <t>Nikunj</t>
+  </si>
+  <si>
+    <t>Pratham</t>
+  </si>
+  <si>
+    <t>Prince</t>
+  </si>
+  <si>
+    <t>Dhobi</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Sanket</t>
+  </si>
+  <si>
+    <t>Pansuriya</t>
+  </si>
+  <si>
+    <t>Vihang</t>
+  </si>
+  <si>
+    <t>Joshi</t>
+  </si>
+  <si>
+    <t>Vivek</t>
+  </si>
+  <si>
+    <t>Yash</t>
+  </si>
+  <si>
+    <t>Zeel</t>
+  </si>
+  <si>
+    <t>Mavani</t>
+  </si>
+  <si>
+    <t>Chandekar</t>
+  </si>
+  <si>
+    <t>Kathiriya</t>
+  </si>
+  <si>
+    <t>Kotiya</t>
+  </si>
+  <si>
+    <t>Palanpuri</t>
+  </si>
+  <si>
+    <t>Akshat</t>
+  </si>
+  <si>
+    <t>Thakkar</t>
+  </si>
+  <si>
+    <t>Bhavnagar</t>
+  </si>
+  <si>
+    <t>Kutch</t>
+  </si>
+  <si>
+    <t>Gandhinagar</t>
+  </si>
+  <si>
+    <t>Bharuch</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -81,8 +240,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,43 +557,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C890F38-87C6-4A50-8BFC-DAAB1C1F1968}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45603</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D30">
+    <sortCondition ref="A2:A30"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>